--- a/data/merged/2026-10-08/MERGED_US_Robot-Vacuum_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_US_Robot-Vacuum_2026-10-08.xlsx
@@ -7256,94 +7256,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7669,7 +7581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -19130,125 +19042,115 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0H8P1935J</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>eufy</t>
+          <t>MAMNV</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.com/stores/MAMNV%E2%80%93EasyCleanSmartLife/page/8D8AAEE8-B33E-4170-A040-EBBE704715A0?lp_asin=B0H8P1935J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>eufy RoboVac Hard Floor Cleaning Solution (2 Bottles), Dilution Ratio 1:200, 473 ml, Floor Cleaner, Plant-Based,Compatible wi</t>
+          <t>Robot Vacuum and Mop for Pet Hair, 11500Pa Suction, 90-Day Self-Emptyings90-Day Hands-Free Cleaning,3-in-1 Vacuum Mop,LiDAR</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/dp/B0C7C7PLLG?psc=1</t>
+          <t>https://www.amazon.com/dp/B0H8P1935J?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41yLA5scgYL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0C7C7PLLG</t>
+          <t>B0H8P1935J</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
+          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
         </is>
       </c>
       <c r="N49" s="14" t="inlineStr">
         <is>
-          <t>Industrial &amp; Scientific</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O49" s="15">
-        <v>2480</v>
+        <v>60987</v>
       </c>
       <c r="P49" s="15">
-        <v>125</v>
+        <v>725582</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.05</v>
+        <v>0.89</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
+          <t>Robotic Vacuums</t>
         </is>
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>4
-22</t>
+          <t>62</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>2246</v>
-      </c>
-      <c r="U49" s="16">
-        <v>0.01</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="U49" s="16"/>
       <c r="V49" s="15">
-        <v>47144</v>
-      </c>
-      <c r="W49" s="15" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="X49" s="15">
-        <v>56940</v>
-      </c>
+        <v>10222</v>
+      </c>
+      <c r="W49" s="15"/>
+      <c r="X49" s="15"/>
       <c r="Y49" s="19">
         <v>2</v>
       </c>
       <c r="Z49" s="20">
-        <v>29.99</v>
+        <v>268.99</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49" s="15"/>
       <c r="AD49" s="19">
-        <v>1521</v>
+        <v>2203</v>
       </c>
       <c r="AE49" s="15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AF49" s="21">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.010700000000000001</v>
+        <v>0</v>
       </c>
       <c r="AH49" s="20">
-        <v>6.31</v>
+        <v>21.23</v>
       </c>
       <c r="AI49" s="16">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2023-06-30</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>1195</v>
+        <v>50</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
@@ -19259,14 +19161,14 @@
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR49" s="19">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Anker EufyHome</t>
+          <t>Woot</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
@@ -19281,12 +19183,12 @@
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>WA 98004 US</t>
+          <t>4121 International Parkway</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3</t>
+          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KWJVS57NX03I</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
@@ -19319,501 +19221,45 @@
       </c>
       <c r="BJ49" s="23" t="inlineStr">
         <is>
-          <t>2.31 pounds</t>
+          <t>14.4 pounds</t>
         </is>
       </c>
       <c r="BK49" s="23" t="inlineStr">
         <is>
-          <t>1.05 kg</t>
+          <t>6.53 kg</t>
         </is>
       </c>
       <c r="BL49" s="23" t="inlineStr">
         <is>
-          <t>8.8 x 4.4 x 2 inches</t>
+          <t>12.59"L x 12.59"W x 3.82"H</t>
         </is>
       </c>
       <c r="BM49" s="23" t="inlineStr">
         <is>
-          <t>22.35 x 11.18 x 5.08 cm</t>
+          <t>31.98 x 31.98 x 9.70 cm</t>
         </is>
       </c>
       <c r="BN49" s="23" t="inlineStr">
         <is>
-          <t>2.38 pounds</t>
+          <t>19.8 pounds</t>
         </is>
       </c>
       <c r="BO49" s="23" t="inlineStr">
         <is>
-          <t>1.08 kg</t>
+          <t>8.98 kg</t>
         </is>
       </c>
       <c r="BP49" s="23" t="inlineStr">
         <is>
-          <t>8.9 x 4.6 x 4 inches</t>
+          <t>16.5 x 15.7 x 13.5 inches</t>
         </is>
       </c>
       <c r="BQ49" s="23" t="inlineStr">
         <is>
-          <t>22.61 x 11.68 x 10.16 cm</t>
+          <t>41.91 x 39.88 x 34.29 cm</t>
         </is>
       </c>
       <c r="BR49" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0BCF8N3B4</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>ECOVACS</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>ECOVACS Multi-Surface Floor Cleaning Solution, Compatible with DEEBOT X11 OMNI Cyclone / X9 PRO OMNI / T80 OMNI / T50 PRO OMN</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0BCF8N3B4?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0BCF8N3B4</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific:Janitorial &amp; Sanitation Supplies:Vacuums &amp; Floor Cleaning Machines:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Industrial &amp; Scientific</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>3146</v>
-      </c>
-      <c r="P50" s="15">
-        <v>-161</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>-0.05</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Commercial Indoor Robotic Vacuums
-Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>5
-24</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>1856</v>
-      </c>
-      <c r="U50" s="16">
-        <v>-0.05</v>
-      </c>
-      <c r="V50" s="15">
-        <v>46381</v>
-      </c>
-      <c r="W50" s="15" t="inlineStr">
-        <is>
-          <t>1,000</t>
-        </is>
-      </c>
-      <c r="X50" s="15">
-        <v>24990</v>
-      </c>
-      <c r="Y50" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>24.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="15">
-        <v>3</v>
-      </c>
-      <c r="AD50" s="19">
-        <v>1229</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>26</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.5</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0.013999999999999999</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>6.48</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.62</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2023-02-17</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>1328</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>8</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>2.69 pounds</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>1.22 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23" t="inlineStr">
-        <is>
-          <t>3.5 x 3.5 x 9.7 inches</t>
-        </is>
-      </c>
-      <c r="BM50" s="23" t="inlineStr">
-        <is>
-          <t>8.89 x 8.89 x 24.64 cm</t>
-        </is>
-      </c>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>2.62 pounds</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>1.19 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>9.7 x 3.5 x 3.5 inches</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>24.64 x 8.89 x 8.89 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>大号标准尺寸</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0H8P1935J</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>MAMNV</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/stores/MAMNV%E2%80%93EasyCleanSmartLife/page/8D8AAEE8-B33E-4170-A040-EBBE704715A0?lp_asin=B0H8P1935J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Robot Vacuum and Mop for Pet Hair, 11500Pa Suction, 90-Day Self-Emptyings90-Day Hands-Free Cleaning,3-in-1 Vacuum Mop,LiDAR</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/dp/B0H8P1935J?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41yLA5scgYL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0H8P1935J</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Vacuums &amp; Floor Care:Vacuums:Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>60987</v>
-      </c>
-      <c r="P51" s="15">
-        <v>725582</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>0.89</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Robotic Vacuums</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>38</v>
-      </c>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15">
-        <v>10222</v>
-      </c>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51" s="19">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>268.99</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="15"/>
-      <c r="AD51" s="19">
-        <v>2203</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>0</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.5</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>21.23</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.77</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>50</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>9</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>7</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Woot</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>4121 International Parkway</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KWJVS57NX03I</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ51" s="23" t="inlineStr">
-        <is>
-          <t>14.4 pounds</t>
-        </is>
-      </c>
-      <c r="BK51" s="23" t="inlineStr">
-        <is>
-          <t>6.53 kg</t>
-        </is>
-      </c>
-      <c r="BL51" s="23" t="inlineStr">
-        <is>
-          <t>12.59"L x 12.59"W x 3.82"H</t>
-        </is>
-      </c>
-      <c r="BM51" s="23" t="inlineStr">
-        <is>
-          <t>31.98 x 31.98 x 9.70 cm</t>
-        </is>
-      </c>
-      <c r="BN51" s="23" t="inlineStr">
-        <is>
-          <t>19.8 pounds</t>
-        </is>
-      </c>
-      <c r="BO51" s="23" t="inlineStr">
-        <is>
-          <t>8.98 kg</t>
-        </is>
-      </c>
-      <c r="BP51" s="23" t="inlineStr">
-        <is>
-          <t>16.5 x 15.7 x 13.5 inches</t>
-        </is>
-      </c>
-      <c r="BQ51" s="23" t="inlineStr">
-        <is>
-          <t>41.91 x 39.88 x 34.29 cm</t>
-        </is>
-      </c>
-      <c r="BR51" s="13" t="inlineStr">
         <is>
           <t>小号大件</t>
         </is>
@@ -20179,31 +19625,16 @@
     <hyperlink ref="L48" r:id="rId354" tooltip="https://www.amazon.com/dp/B0DDYZ4VK4"/>
     <hyperlink ref="M48" r:id="rId355" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N48" r:id="rId356"/>
-    <hyperlink ref="C49" r:id="rId357" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="G49" r:id="rId358" tooltip="https://www.amazon.com/stores/eufy/page/B02CB877-324C-4130-B1A3-41E418F2C467?lp_asin=B0C7C7PLLG&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J49" r:id="rId359" tooltip="https://www.amazon.com/dp/B0C7C7PLLG?psc=1"/>
-    <hyperlink ref="K49" r:id="rId360" tooltip="https://images-na.ssl-images-amazon.com/images/I/511jqutQR2L._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId361" tooltip="https://www.amazon.com/dp/B0C7C7PLLG"/>
-    <hyperlink ref="M49" r:id="rId362" tooltip="https://www.amazon.com/b?node=3256980011"/>
+    <hyperlink ref="C49" r:id="rId357" tooltip="https://www.amazon.com/dp/B0H8P1935J"/>
+    <hyperlink ref="G49" r:id="rId358" tooltip="https://www.amazon.com/stores/MAMNV%E2%80%93EasyCleanSmartLife/page/8D8AAEE8-B33E-4170-A040-EBBE704715A0?lp_asin=B0H8P1935J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J49" r:id="rId359" tooltip="https://www.amazon.com/dp/B0H8P1935J?psc=1"/>
+    <hyperlink ref="K49" r:id="rId360" tooltip="https://m.media-amazon.com/images/I/41yLA5scgYL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId361" tooltip="https://www.amazon.com/dp/B0H8P1935J"/>
+    <hyperlink ref="M49" r:id="rId362" tooltip="https://www.amazon.com/b?node=3743561"/>
     <hyperlink ref="N49" r:id="rId363"/>
-    <hyperlink ref="AW49" r:id="rId364" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1U62USFOR8NN3"/>
-    <hyperlink ref="C50" r:id="rId365" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="G50" r:id="rId366" tooltip="https://www.amazon.com/stores/ECOVACS/page/E74F14EC-79FC-433B-8BB9-DA6190E35D28?lp_asin=B0BCF8N3B4&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId367" tooltip="https://www.amazon.com/dp/B0BCF8N3B4?psc=1"/>
-    <hyperlink ref="K50" r:id="rId368" tooltip="https://images-na.ssl-images-amazon.com/images/I/51OKmAG4ODL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId369" tooltip="https://www.amazon.com/dp/B0BCF8N3B4"/>
-    <hyperlink ref="M50" r:id="rId370" tooltip="https://www.amazon.com/b?node=3256980011"/>
-    <hyperlink ref="N50" r:id="rId371"/>
-    <hyperlink ref="C51" r:id="rId372" tooltip="https://www.amazon.com/dp/B0H8P1935J"/>
-    <hyperlink ref="G51" r:id="rId373" tooltip="https://www.amazon.com/stores/MAMNV%E2%80%93EasyCleanSmartLife/page/8D8AAEE8-B33E-4170-A040-EBBE704715A0?lp_asin=B0H8P1935J&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J51" r:id="rId374" tooltip="https://www.amazon.com/dp/B0H8P1935J?psc=1"/>
-    <hyperlink ref="K51" r:id="rId375" tooltip="https://m.media-amazon.com/images/I/41yLA5scgYL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId376" tooltip="https://www.amazon.com/dp/B0H8P1935J"/>
-    <hyperlink ref="M51" r:id="rId377" tooltip="https://www.amazon.com/b?node=3743561"/>
-    <hyperlink ref="N51" r:id="rId378"/>
-    <hyperlink ref="AW51" r:id="rId379" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KWJVS57NX03I"/>
+    <hyperlink ref="AW49" r:id="rId364" tooltip="https://www.amazon.com/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1KWJVS57NX03I"/>
   </hyperlinks>
-  <drawing r:id="rId380"/>
+  <drawing r:id="rId365"/>
 </worksheet>
 </file>
 
@@ -20273,7 +19704,7 @@
         <v>525.9440483497805</v>
       </c>
       <c r="G2" s="22">
-        <v>0.16810731436282098</v>
+        <v>0.17376500414331777</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20294,7 +19725,7 @@
         <v>318.2218317326628</v>
       </c>
       <c r="G3" s="22">
-        <v>0.2619915069254276</v>
+        <v>0.270808890493342</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20315,7 +19746,7 @@
         <v>293.39125598491074</v>
       </c>
       <c r="G4" s="22">
-        <v>0.16412271302139145</v>
+        <v>0.1696463001402985</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20336,7 +19767,7 @@
         <v>459.6164812942366</v>
       </c>
       <c r="G5" s="22">
-        <v>0.07850140889788466</v>
+        <v>0.08114339161326846</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20346,18 +19777,18 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <v>10648</v>
+        <v>8402</v>
       </c>
       <c r="C6" s="15">
-        <v>2733249</v>
+        <v>2686105</v>
       </c>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="20">
-        <v>256.6913035311796</v>
+        <v>319.6982861223518</v>
       </c>
       <c r="G6" s="22">
-        <v>0.08451799817438584</v>
+        <v>0.06893496221786467</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20367,18 +19798,18 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <v>7034</v>
+        <v>5178</v>
       </c>
       <c r="C7" s="15">
-        <v>2372681</v>
+        <v>2326300</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
       <c r="F7" s="20">
-        <v>337.31603639465453</v>
+        <v>449.2661259173426</v>
       </c>
       <c r="G7" s="22">
-        <v>0.05583204349724173</v>
+        <v>0.042483365194489794</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20399,7 +19830,7 @@
         <v>519.64329004329</v>
       </c>
       <c r="G8" s="22">
-        <v>0.018335516132872962</v>
+        <v>0.018952602085606687</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20420,7 +19851,7 @@
         <v>94.98995145082985</v>
       </c>
       <c r="G9" s="22">
-        <v>0.07030202008175576</v>
+        <v>0.07266805050745387</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20441,7 +19872,7 @@
         <v>127.0631987223363</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03478985593523039</v>
+        <v>0.035960716424768016</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20462,7 +19893,7 @@
         <v>88.53090739444833</v>
       </c>
       <c r="G11" s="22">
-        <v>0.03402786045957852</v>
+        <v>0.03517307581861293</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20483,7 +19914,7 @@
         <v>559.9896602658789</v>
       </c>
       <c r="G12" s="22">
-        <v>0.005373655593919911</v>
+        <v>0.005554507191322826</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20504,7 +19935,7 @@
         <v>1044.9912280701753</v>
       </c>
       <c r="G13" s="22">
-        <v>0.0027146088820097633</v>
+        <v>0.0028059696594274837</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20525,7 +19956,7 @@
         <v>97.8019578313253</v>
       </c>
       <c r="G14" s="22">
-        <v>0.021081874826368217</v>
+        <v>0.021791390103623968</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20546,7 +19977,7 @@
         <v>269.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.00030162320911219587</v>
+        <v>0.00031177440660305376</v>
       </c>
     </row>
   </sheetData>
@@ -20610,18 +20041,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>46656</v>
+        <v>44800</v>
       </c>
       <c r="C2" s="15">
-        <v>15295603</v>
+        <v>15249222</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>327.83785579561044</v>
+        <v>340.38441964285715</v>
       </c>
       <c r="G2" s="22">
-        <v>0.3703298011668056</v>
+        <v>0.3675656162057055</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20642,7 +20073,7 @@
         <v>525.9440483497805</v>
       </c>
       <c r="G3" s="22">
-        <v>0.16810731436282098</v>
+        <v>0.17376500414331777</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20663,7 +20094,7 @@
         <v>332.1592940377871</v>
       </c>
       <c r="G4" s="22">
-        <v>0.14031829186014208</v>
+        <v>0.14504073578759957</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20673,18 +20104,18 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <v>10648</v>
+        <v>8402</v>
       </c>
       <c r="C5" s="15">
-        <v>2733249</v>
+        <v>2686105</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="20">
-        <v>256.6913035311796</v>
+        <v>319.6982861223518</v>
       </c>
       <c r="G5" s="22">
-        <v>0.08451799817438584</v>
+        <v>0.06893496221786467</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20705,7 +20136,7 @@
         <v>398.9899756163641</v>
       </c>
       <c r="G6" s="22">
-        <v>0.02929713854823987</v>
+        <v>0.03028314038873346</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20726,7 +20157,7 @@
         <v>94.98995145082985</v>
       </c>
       <c r="G7" s="22">
-        <v>0.07030202008175576</v>
+        <v>0.07266805050745387</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20747,7 +20178,7 @@
         <v>469.9902786779002</v>
       </c>
       <c r="G8" s="22">
-        <v>0.012247489780529428</v>
+        <v>0.012659681826013472</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20768,7 +20199,7 @@
         <v>823.3798882681564</v>
       </c>
       <c r="G9" s="22">
-        <v>0.00568321625590348</v>
+        <v>0.005874486187573328</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20789,7 +20220,7 @@
         <v>127.0631987223363</v>
       </c>
       <c r="G10" s="22">
-        <v>0.03478985593523039</v>
+        <v>0.035960716424768016</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20810,7 +20241,7 @@
         <v>359.9903381642512</v>
       </c>
       <c r="G11" s="22">
-        <v>0.011501369210620312</v>
+        <v>0.011888450399153287</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20831,7 +20262,7 @@
         <v>544.5244755244755</v>
       </c>
       <c r="G12" s="22">
-        <v>0.005675278803032107</v>
+        <v>0.00586628159792588</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20852,7 +20283,7 @@
         <v>88.53090739444833</v>
       </c>
       <c r="G13" s="22">
-        <v>0.03402786045957852</v>
+        <v>0.03517307581861293</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20873,7 +20304,7 @@
         <v>1044.9912280701753</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0027146088820097633</v>
+        <v>0.0028059696594274837</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20894,7 +20325,7 @@
         <v>179.0</v>
       </c>
       <c r="G15" s="22">
-        <v>0.009405881652577688</v>
+        <v>0.009722438732226807</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20915,7 +20346,7 @@
         <v>85.4799186578546</v>
       </c>
       <c r="G16" s="22">
-        <v>0.015612969797991825</v>
+        <v>0.016138427836531757</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20936,7 +20367,7 @@
         <v>132.97968069666183</v>
       </c>
       <c r="G17" s="22">
-        <v>0.005468905028376394</v>
+        <v>0.005652962267092211</v>
       </c>
     </row>
   </sheetData>
